--- a/files/temp_files/statement_2026_09.xlsx
+++ b/files/temp_files/statement_2026_09.xlsx
@@ -591,7 +591,7 @@
         <v>34</v>
       </c>
       <c r="C2">
-        <v>89.48</v>
+        <v>-89.48</v>
       </c>
       <c r="D2" t="s">
         <v>57</v>
@@ -605,7 +605,7 @@
         <v>35</v>
       </c>
       <c r="C3">
-        <v>30.37</v>
+        <v>-30.37</v>
       </c>
       <c r="D3" t="s">
         <v>58</v>
@@ -619,7 +619,7 @@
         <v>36</v>
       </c>
       <c r="C4">
-        <v>45.46</v>
+        <v>-45.46</v>
       </c>
       <c r="D4" t="s">
         <v>59</v>
@@ -633,7 +633,7 @@
         <v>37</v>
       </c>
       <c r="C5">
-        <v>27.02</v>
+        <v>-27.02</v>
       </c>
       <c r="D5" t="s">
         <v>60</v>
@@ -661,7 +661,7 @@
         <v>34</v>
       </c>
       <c r="C7">
-        <v>29.31</v>
+        <v>-29.31</v>
       </c>
       <c r="D7" t="s">
         <v>57</v>
@@ -675,7 +675,7 @@
         <v>39</v>
       </c>
       <c r="C8">
-        <v>257.85</v>
+        <v>-257.85</v>
       </c>
       <c r="D8" t="s">
         <v>58</v>
@@ -689,7 +689,7 @@
         <v>40</v>
       </c>
       <c r="C9">
-        <v>93.55</v>
+        <v>-93.55</v>
       </c>
       <c r="D9" t="s">
         <v>60</v>
@@ -703,7 +703,7 @@
         <v>41</v>
       </c>
       <c r="C10">
-        <v>14.98</v>
+        <v>-14.98</v>
       </c>
       <c r="D10" t="s">
         <v>62</v>
@@ -717,7 +717,7 @@
         <v>42</v>
       </c>
       <c r="C11">
-        <v>302.87</v>
+        <v>-302.87</v>
       </c>
       <c r="D11" t="s">
         <v>63</v>
@@ -731,7 +731,7 @@
         <v>36</v>
       </c>
       <c r="C12">
-        <v>143.66</v>
+        <v>-143.66</v>
       </c>
       <c r="D12" t="s">
         <v>59</v>
@@ -745,7 +745,7 @@
         <v>43</v>
       </c>
       <c r="C13">
-        <v>178.37</v>
+        <v>-178.37</v>
       </c>
       <c r="D13" t="s">
         <v>64</v>
@@ -759,7 +759,7 @@
         <v>44</v>
       </c>
       <c r="C14">
-        <v>21.26</v>
+        <v>-21.26</v>
       </c>
       <c r="D14" t="s">
         <v>62</v>
@@ -773,7 +773,7 @@
         <v>41</v>
       </c>
       <c r="C15">
-        <v>6.59</v>
+        <v>-6.59</v>
       </c>
       <c r="D15" t="s">
         <v>62</v>
@@ -787,7 +787,7 @@
         <v>36</v>
       </c>
       <c r="C16">
-        <v>142.47</v>
+        <v>-142.47</v>
       </c>
       <c r="D16" t="s">
         <v>59</v>
@@ -815,7 +815,7 @@
         <v>37</v>
       </c>
       <c r="C18">
-        <v>30.23</v>
+        <v>-30.23</v>
       </c>
       <c r="D18" t="s">
         <v>60</v>
@@ -829,7 +829,7 @@
         <v>46</v>
       </c>
       <c r="C19">
-        <v>69.09999999999999</v>
+        <v>-69.09999999999999</v>
       </c>
       <c r="D19" t="s">
         <v>64</v>
@@ -857,7 +857,7 @@
         <v>48</v>
       </c>
       <c r="C21">
-        <v>687.4</v>
+        <v>-687.4</v>
       </c>
       <c r="D21" t="s">
         <v>63</v>
@@ -885,7 +885,7 @@
         <v>41</v>
       </c>
       <c r="C23">
-        <v>44.1</v>
+        <v>-44.1</v>
       </c>
       <c r="D23" t="s">
         <v>62</v>
@@ -913,7 +913,7 @@
         <v>34</v>
       </c>
       <c r="C25">
-        <v>289.34</v>
+        <v>-289.34</v>
       </c>
       <c r="D25" t="s">
         <v>57</v>
@@ -927,7 +927,7 @@
         <v>36</v>
       </c>
       <c r="C26">
-        <v>51.13</v>
+        <v>-51.13</v>
       </c>
       <c r="D26" t="s">
         <v>59</v>
@@ -955,7 +955,7 @@
         <v>49</v>
       </c>
       <c r="C28">
-        <v>96.95999999999999</v>
+        <v>-96.95999999999999</v>
       </c>
       <c r="D28" t="s">
         <v>57</v>
@@ -969,7 +969,7 @@
         <v>50</v>
       </c>
       <c r="C29">
-        <v>125.83</v>
+        <v>-125.83</v>
       </c>
       <c r="D29" t="s">
         <v>64</v>
@@ -983,7 +983,7 @@
         <v>51</v>
       </c>
       <c r="C30">
-        <v>271.95</v>
+        <v>-271.95</v>
       </c>
       <c r="D30" t="s">
         <v>57</v>
@@ -997,7 +997,7 @@
         <v>44</v>
       </c>
       <c r="C31">
-        <v>38.22</v>
+        <v>-38.22</v>
       </c>
       <c r="D31" t="s">
         <v>62</v>
@@ -1011,7 +1011,7 @@
         <v>46</v>
       </c>
       <c r="C32">
-        <v>175.49</v>
+        <v>-175.49</v>
       </c>
       <c r="D32" t="s">
         <v>64</v>
@@ -1025,7 +1025,7 @@
         <v>52</v>
       </c>
       <c r="C33">
-        <v>6.16</v>
+        <v>-6.16</v>
       </c>
       <c r="D33" t="s">
         <v>62</v>
@@ -1039,7 +1039,7 @@
         <v>53</v>
       </c>
       <c r="C34">
-        <v>208.55</v>
+        <v>-208.55</v>
       </c>
       <c r="D34" t="s">
         <v>58</v>
@@ -1053,7 +1053,7 @@
         <v>46</v>
       </c>
       <c r="C35">
-        <v>184.54</v>
+        <v>-184.54</v>
       </c>
       <c r="D35" t="s">
         <v>64</v>
@@ -1067,7 +1067,7 @@
         <v>46</v>
       </c>
       <c r="C36">
-        <v>168.85</v>
+        <v>-168.85</v>
       </c>
       <c r="D36" t="s">
         <v>64</v>
@@ -1095,7 +1095,7 @@
         <v>41</v>
       </c>
       <c r="C38">
-        <v>18.99</v>
+        <v>-18.99</v>
       </c>
       <c r="D38" t="s">
         <v>62</v>
@@ -1123,7 +1123,7 @@
         <v>42</v>
       </c>
       <c r="C40">
-        <v>758.67</v>
+        <v>-758.67</v>
       </c>
       <c r="D40" t="s">
         <v>63</v>
@@ -1137,7 +1137,7 @@
         <v>40</v>
       </c>
       <c r="C41">
-        <v>90.69</v>
+        <v>-90.69</v>
       </c>
       <c r="D41" t="s">
         <v>60</v>
@@ -1151,7 +1151,7 @@
         <v>48</v>
       </c>
       <c r="C42">
-        <v>426.05</v>
+        <v>-426.05</v>
       </c>
       <c r="D42" t="s">
         <v>63</v>
@@ -1165,7 +1165,7 @@
         <v>52</v>
       </c>
       <c r="C43">
-        <v>24.38</v>
+        <v>-24.38</v>
       </c>
       <c r="D43" t="s">
         <v>62</v>
@@ -1179,7 +1179,7 @@
         <v>34</v>
       </c>
       <c r="C44">
-        <v>308.58</v>
+        <v>-308.58</v>
       </c>
       <c r="D44" t="s">
         <v>57</v>
@@ -1193,7 +1193,7 @@
         <v>54</v>
       </c>
       <c r="C45">
-        <v>61.49</v>
+        <v>-61.49</v>
       </c>
       <c r="D45" t="s">
         <v>59</v>
@@ -1207,7 +1207,7 @@
         <v>49</v>
       </c>
       <c r="C46">
-        <v>376.1</v>
+        <v>-376.1</v>
       </c>
       <c r="D46" t="s">
         <v>57</v>
@@ -1221,7 +1221,7 @@
         <v>48</v>
       </c>
       <c r="C47">
-        <v>348.3</v>
+        <v>-348.3</v>
       </c>
       <c r="D47" t="s">
         <v>63</v>
@@ -1235,7 +1235,7 @@
         <v>54</v>
       </c>
       <c r="C48">
-        <v>80.45</v>
+        <v>-80.45</v>
       </c>
       <c r="D48" t="s">
         <v>59</v>
@@ -1249,7 +1249,7 @@
         <v>37</v>
       </c>
       <c r="C49">
-        <v>28.74</v>
+        <v>-28.74</v>
       </c>
       <c r="D49" t="s">
         <v>60</v>
@@ -1277,7 +1277,7 @@
         <v>42</v>
       </c>
       <c r="C51">
-        <v>976.42</v>
+        <v>-976.42</v>
       </c>
       <c r="D51" t="s">
         <v>63</v>
@@ -1291,7 +1291,7 @@
         <v>35</v>
       </c>
       <c r="C52">
-        <v>201.8</v>
+        <v>-201.8</v>
       </c>
       <c r="D52" t="s">
         <v>58</v>
@@ -1305,7 +1305,7 @@
         <v>44</v>
       </c>
       <c r="C53">
-        <v>14.63</v>
+        <v>-14.63</v>
       </c>
       <c r="D53" t="s">
         <v>62</v>
@@ -1319,7 +1319,7 @@
         <v>43</v>
       </c>
       <c r="C54">
-        <v>172.31</v>
+        <v>-172.31</v>
       </c>
       <c r="D54" t="s">
         <v>64</v>
@@ -1333,7 +1333,7 @@
         <v>34</v>
       </c>
       <c r="C55">
-        <v>442.97</v>
+        <v>-442.97</v>
       </c>
       <c r="D55" t="s">
         <v>57</v>
@@ -1347,7 +1347,7 @@
         <v>51</v>
       </c>
       <c r="C56">
-        <v>307.63</v>
+        <v>-307.63</v>
       </c>
       <c r="D56" t="s">
         <v>57</v>
@@ -1361,7 +1361,7 @@
         <v>52</v>
       </c>
       <c r="C57">
-        <v>31.66</v>
+        <v>-31.66</v>
       </c>
       <c r="D57" t="s">
         <v>62</v>
@@ -1375,7 +1375,7 @@
         <v>52</v>
       </c>
       <c r="C58">
-        <v>29.94</v>
+        <v>-29.94</v>
       </c>
       <c r="D58" t="s">
         <v>62</v>
@@ -1403,7 +1403,7 @@
         <v>53</v>
       </c>
       <c r="C60">
-        <v>122.22</v>
+        <v>-122.22</v>
       </c>
       <c r="D60" t="s">
         <v>58</v>
@@ -1417,7 +1417,7 @@
         <v>35</v>
       </c>
       <c r="C61">
-        <v>285.53</v>
+        <v>-285.53</v>
       </c>
       <c r="D61" t="s">
         <v>58</v>
@@ -1431,7 +1431,7 @@
         <v>49</v>
       </c>
       <c r="C62">
-        <v>114.05</v>
+        <v>-114.05</v>
       </c>
       <c r="D62" t="s">
         <v>57</v>
@@ -1445,7 +1445,7 @@
         <v>48</v>
       </c>
       <c r="C63">
-        <v>917.11</v>
+        <v>-917.11</v>
       </c>
       <c r="D63" t="s">
         <v>63</v>
@@ -1459,7 +1459,7 @@
         <v>44</v>
       </c>
       <c r="C64">
-        <v>41.36</v>
+        <v>-41.36</v>
       </c>
       <c r="D64" t="s">
         <v>62</v>
@@ -1501,7 +1501,7 @@
         <v>42</v>
       </c>
       <c r="C67">
-        <v>856.9400000000001</v>
+        <v>-856.9400000000001</v>
       </c>
       <c r="D67" t="s">
         <v>63</v>
@@ -1515,7 +1515,7 @@
         <v>36</v>
       </c>
       <c r="C68">
-        <v>82.45999999999999</v>
+        <v>-82.45999999999999</v>
       </c>
       <c r="D68" t="s">
         <v>59</v>
@@ -1529,7 +1529,7 @@
         <v>41</v>
       </c>
       <c r="C69">
-        <v>30.78</v>
+        <v>-30.78</v>
       </c>
       <c r="D69" t="s">
         <v>62</v>
@@ -1543,7 +1543,7 @@
         <v>54</v>
       </c>
       <c r="C70">
-        <v>72.05</v>
+        <v>-72.05</v>
       </c>
       <c r="D70" t="s">
         <v>59</v>
@@ -1557,7 +1557,7 @@
         <v>50</v>
       </c>
       <c r="C71">
-        <v>118.68</v>
+        <v>-118.68</v>
       </c>
       <c r="D71" t="s">
         <v>64</v>
@@ -1571,7 +1571,7 @@
         <v>53</v>
       </c>
       <c r="C72">
-        <v>271.45</v>
+        <v>-271.45</v>
       </c>
       <c r="D72" t="s">
         <v>58</v>
@@ -1585,7 +1585,7 @@
         <v>41</v>
       </c>
       <c r="C73">
-        <v>43.95</v>
+        <v>-43.95</v>
       </c>
       <c r="D73" t="s">
         <v>62</v>
@@ -1599,7 +1599,7 @@
         <v>39</v>
       </c>
       <c r="C74">
-        <v>131.25</v>
+        <v>-131.25</v>
       </c>
       <c r="D74" t="s">
         <v>58</v>
@@ -1613,7 +1613,7 @@
         <v>46</v>
       </c>
       <c r="C75">
-        <v>128.43</v>
+        <v>-128.43</v>
       </c>
       <c r="D75" t="s">
         <v>64</v>
@@ -1641,7 +1641,7 @@
         <v>43</v>
       </c>
       <c r="C77">
-        <v>114.27</v>
+        <v>-114.27</v>
       </c>
       <c r="D77" t="s">
         <v>64</v>
@@ -1655,7 +1655,7 @@
         <v>35</v>
       </c>
       <c r="C78">
-        <v>232.44</v>
+        <v>-232.44</v>
       </c>
       <c r="D78" t="s">
         <v>58</v>
@@ -1669,7 +1669,7 @@
         <v>41</v>
       </c>
       <c r="C79">
-        <v>29.6</v>
+        <v>-29.6</v>
       </c>
       <c r="D79" t="s">
         <v>62</v>
@@ -1683,7 +1683,7 @@
         <v>43</v>
       </c>
       <c r="C80">
-        <v>94.69</v>
+        <v>-94.69</v>
       </c>
       <c r="D80" t="s">
         <v>64</v>
@@ -1711,7 +1711,7 @@
         <v>48</v>
       </c>
       <c r="C82">
-        <v>283.83</v>
+        <v>-283.83</v>
       </c>
       <c r="D82" t="s">
         <v>63</v>
@@ -1725,7 +1725,7 @@
         <v>52</v>
       </c>
       <c r="C83">
-        <v>26.29</v>
+        <v>-26.29</v>
       </c>
       <c r="D83" t="s">
         <v>62</v>
@@ -1739,7 +1739,7 @@
         <v>37</v>
       </c>
       <c r="C84">
-        <v>41.99</v>
+        <v>-41.99</v>
       </c>
       <c r="D84" t="s">
         <v>60</v>
@@ -1753,7 +1753,7 @@
         <v>55</v>
       </c>
       <c r="C85">
-        <v>141.44</v>
+        <v>-141.44</v>
       </c>
       <c r="D85" t="s">
         <v>59</v>
@@ -1767,7 +1767,7 @@
         <v>50</v>
       </c>
       <c r="C86">
-        <v>134.76</v>
+        <v>-134.76</v>
       </c>
       <c r="D86" t="s">
         <v>64</v>
@@ -1781,7 +1781,7 @@
         <v>36</v>
       </c>
       <c r="C87">
-        <v>58.9</v>
+        <v>-58.9</v>
       </c>
       <c r="D87" t="s">
         <v>59</v>
@@ -1795,7 +1795,7 @@
         <v>52</v>
       </c>
       <c r="C88">
-        <v>10.17</v>
+        <v>-10.17</v>
       </c>
       <c r="D88" t="s">
         <v>62</v>
@@ -1809,7 +1809,7 @@
         <v>40</v>
       </c>
       <c r="C89">
-        <v>14.67</v>
+        <v>-14.67</v>
       </c>
       <c r="D89" t="s">
         <v>60</v>
@@ -1823,7 +1823,7 @@
         <v>42</v>
       </c>
       <c r="C90">
-        <v>501.17</v>
+        <v>-501.17</v>
       </c>
       <c r="D90" t="s">
         <v>63</v>
@@ -1837,7 +1837,7 @@
         <v>44</v>
       </c>
       <c r="C91">
-        <v>24.67</v>
+        <v>-24.67</v>
       </c>
       <c r="D91" t="s">
         <v>62</v>
@@ -1865,7 +1865,7 @@
         <v>36</v>
       </c>
       <c r="C93">
-        <v>107.5</v>
+        <v>-107.5</v>
       </c>
       <c r="D93" t="s">
         <v>59</v>
@@ -1879,7 +1879,7 @@
         <v>51</v>
       </c>
       <c r="C94">
-        <v>170.76</v>
+        <v>-170.76</v>
       </c>
       <c r="D94" t="s">
         <v>57</v>
@@ -1893,7 +1893,7 @@
         <v>51</v>
       </c>
       <c r="C95">
-        <v>457.59</v>
+        <v>-457.59</v>
       </c>
       <c r="D95" t="s">
         <v>57</v>
@@ -1907,7 +1907,7 @@
         <v>40</v>
       </c>
       <c r="C96">
-        <v>74.17</v>
+        <v>-74.17</v>
       </c>
       <c r="D96" t="s">
         <v>60</v>
@@ -1921,7 +1921,7 @@
         <v>39</v>
       </c>
       <c r="C97">
-        <v>274.81</v>
+        <v>-274.81</v>
       </c>
       <c r="D97" t="s">
         <v>58</v>
@@ -1935,7 +1935,7 @@
         <v>40</v>
       </c>
       <c r="C98">
-        <v>67.79000000000001</v>
+        <v>-67.79000000000001</v>
       </c>
       <c r="D98" t="s">
         <v>60</v>
@@ -1949,7 +1949,7 @@
         <v>43</v>
       </c>
       <c r="C99">
-        <v>190.07</v>
+        <v>-190.07</v>
       </c>
       <c r="D99" t="s">
         <v>64</v>
@@ -1991,7 +1991,7 @@
         <v>51</v>
       </c>
       <c r="C102">
-        <v>424.61</v>
+        <v>-424.61</v>
       </c>
       <c r="D102" t="s">
         <v>57</v>
@@ -2005,7 +2005,7 @@
         <v>42</v>
       </c>
       <c r="C103">
-        <v>143.26</v>
+        <v>-143.26</v>
       </c>
       <c r="D103" t="s">
         <v>63</v>
@@ -2019,7 +2019,7 @@
         <v>51</v>
       </c>
       <c r="C104">
-        <v>219.31</v>
+        <v>-219.31</v>
       </c>
       <c r="D104" t="s">
         <v>57</v>
@@ -2033,7 +2033,7 @@
         <v>44</v>
       </c>
       <c r="C105">
-        <v>33.93</v>
+        <v>-33.93</v>
       </c>
       <c r="D105" t="s">
         <v>62</v>
@@ -2047,7 +2047,7 @@
         <v>46</v>
       </c>
       <c r="C106">
-        <v>111.85</v>
+        <v>-111.85</v>
       </c>
       <c r="D106" t="s">
         <v>64</v>
@@ -2075,7 +2075,7 @@
         <v>35</v>
       </c>
       <c r="C108">
-        <v>280.05</v>
+        <v>-280.05</v>
       </c>
       <c r="D108" t="s">
         <v>58</v>
@@ -2089,7 +2089,7 @@
         <v>35</v>
       </c>
       <c r="C109">
-        <v>71.54000000000001</v>
+        <v>-71.54000000000001</v>
       </c>
       <c r="D109" t="s">
         <v>58</v>
@@ -2103,7 +2103,7 @@
         <v>53</v>
       </c>
       <c r="C110">
-        <v>231.44</v>
+        <v>-231.44</v>
       </c>
       <c r="D110" t="s">
         <v>58</v>
@@ -2117,7 +2117,7 @@
         <v>34</v>
       </c>
       <c r="C111">
-        <v>115.73</v>
+        <v>-115.73</v>
       </c>
       <c r="D111" t="s">
         <v>57</v>
@@ -2131,7 +2131,7 @@
         <v>52</v>
       </c>
       <c r="C112">
-        <v>5.14</v>
+        <v>-5.14</v>
       </c>
       <c r="D112" t="s">
         <v>62</v>
@@ -2145,7 +2145,7 @@
         <v>52</v>
       </c>
       <c r="C113">
-        <v>44.42</v>
+        <v>-44.42</v>
       </c>
       <c r="D113" t="s">
         <v>62</v>
@@ -2159,7 +2159,7 @@
         <v>54</v>
       </c>
       <c r="C114">
-        <v>26.86</v>
+        <v>-26.86</v>
       </c>
       <c r="D114" t="s">
         <v>59</v>
@@ -2173,7 +2173,7 @@
         <v>49</v>
       </c>
       <c r="C115">
-        <v>477.96</v>
+        <v>-477.96</v>
       </c>
       <c r="D115" t="s">
         <v>57</v>
@@ -2187,7 +2187,7 @@
         <v>36</v>
       </c>
       <c r="C116">
-        <v>109.81</v>
+        <v>-109.81</v>
       </c>
       <c r="D116" t="s">
         <v>59</v>
@@ -2201,7 +2201,7 @@
         <v>34</v>
       </c>
       <c r="C117">
-        <v>397.66</v>
+        <v>-397.66</v>
       </c>
       <c r="D117" t="s">
         <v>57</v>
@@ -2215,7 +2215,7 @@
         <v>54</v>
       </c>
       <c r="C118">
-        <v>32.56</v>
+        <v>-32.56</v>
       </c>
       <c r="D118" t="s">
         <v>59</v>
@@ -2229,7 +2229,7 @@
         <v>44</v>
       </c>
       <c r="C119">
-        <v>25.64</v>
+        <v>-25.64</v>
       </c>
       <c r="D119" t="s">
         <v>62</v>
@@ -2243,7 +2243,7 @@
         <v>52</v>
       </c>
       <c r="C120">
-        <v>25.8</v>
+        <v>-25.8</v>
       </c>
       <c r="D120" t="s">
         <v>62</v>
@@ -2257,7 +2257,7 @@
         <v>53</v>
       </c>
       <c r="C121">
-        <v>86.45999999999999</v>
+        <v>-86.45999999999999</v>
       </c>
       <c r="D121" t="s">
         <v>58</v>
@@ -2271,7 +2271,7 @@
         <v>40</v>
       </c>
       <c r="C122">
-        <v>14.1</v>
+        <v>-14.1</v>
       </c>
       <c r="D122" t="s">
         <v>60</v>
@@ -2285,7 +2285,7 @@
         <v>48</v>
       </c>
       <c r="C123">
-        <v>955.5700000000001</v>
+        <v>-955.5700000000001</v>
       </c>
       <c r="D123" t="s">
         <v>63</v>
@@ -2299,7 +2299,7 @@
         <v>41</v>
       </c>
       <c r="C124">
-        <v>28.91</v>
+        <v>-28.91</v>
       </c>
       <c r="D124" t="s">
         <v>62</v>
@@ -2313,7 +2313,7 @@
         <v>49</v>
       </c>
       <c r="C125">
-        <v>10.36</v>
+        <v>-10.36</v>
       </c>
       <c r="D125" t="s">
         <v>57</v>
@@ -2327,7 +2327,7 @@
         <v>56</v>
       </c>
       <c r="C126">
-        <v>87.92</v>
+        <v>-87.92</v>
       </c>
       <c r="D126" t="s">
         <v>60</v>
@@ -2341,7 +2341,7 @@
         <v>39</v>
       </c>
       <c r="C127">
-        <v>160.05</v>
+        <v>-160.05</v>
       </c>
       <c r="D127" t="s">
         <v>58</v>
@@ -2355,7 +2355,7 @@
         <v>35</v>
       </c>
       <c r="C128">
-        <v>101.82</v>
+        <v>-101.82</v>
       </c>
       <c r="D128" t="s">
         <v>58</v>
@@ -2369,7 +2369,7 @@
         <v>41</v>
       </c>
       <c r="C129">
-        <v>3.42</v>
+        <v>-3.42</v>
       </c>
       <c r="D129" t="s">
         <v>62</v>
@@ -2383,7 +2383,7 @@
         <v>55</v>
       </c>
       <c r="C130">
-        <v>138.11</v>
+        <v>-138.11</v>
       </c>
       <c r="D130" t="s">
         <v>59</v>
@@ -2411,7 +2411,7 @@
         <v>40</v>
       </c>
       <c r="C132">
-        <v>63.13</v>
+        <v>-63.13</v>
       </c>
       <c r="D132" t="s">
         <v>60</v>
@@ -2425,7 +2425,7 @@
         <v>51</v>
       </c>
       <c r="C133">
-        <v>346.35</v>
+        <v>-346.35</v>
       </c>
       <c r="D133" t="s">
         <v>57</v>
@@ -2439,7 +2439,7 @@
         <v>53</v>
       </c>
       <c r="C134">
-        <v>145.24</v>
+        <v>-145.24</v>
       </c>
       <c r="D134" t="s">
         <v>58</v>
@@ -2467,7 +2467,7 @@
         <v>52</v>
       </c>
       <c r="C136">
-        <v>15.66</v>
+        <v>-15.66</v>
       </c>
       <c r="D136" t="s">
         <v>62</v>
@@ -2495,7 +2495,7 @@
         <v>36</v>
       </c>
       <c r="C138">
-        <v>55.37</v>
+        <v>-55.37</v>
       </c>
       <c r="D138" t="s">
         <v>59</v>
@@ -2523,7 +2523,7 @@
         <v>35</v>
       </c>
       <c r="C140">
-        <v>162.3</v>
+        <v>-162.3</v>
       </c>
       <c r="D140" t="s">
         <v>58</v>
@@ -2537,7 +2537,7 @@
         <v>35</v>
       </c>
       <c r="C141">
-        <v>189.26</v>
+        <v>-189.26</v>
       </c>
       <c r="D141" t="s">
         <v>58</v>
@@ -2565,7 +2565,7 @@
         <v>46</v>
       </c>
       <c r="C143">
-        <v>156.52</v>
+        <v>-156.52</v>
       </c>
       <c r="D143" t="s">
         <v>64</v>
@@ -2579,7 +2579,7 @@
         <v>43</v>
       </c>
       <c r="C144">
-        <v>102.02</v>
+        <v>-102.02</v>
       </c>
       <c r="D144" t="s">
         <v>64</v>
@@ -2593,7 +2593,7 @@
         <v>51</v>
       </c>
       <c r="C145">
-        <v>99.45999999999999</v>
+        <v>-99.45999999999999</v>
       </c>
       <c r="D145" t="s">
         <v>57</v>
@@ -2607,7 +2607,7 @@
         <v>49</v>
       </c>
       <c r="C146">
-        <v>276.87</v>
+        <v>-276.87</v>
       </c>
       <c r="D146" t="s">
         <v>57</v>
@@ -2621,7 +2621,7 @@
         <v>55</v>
       </c>
       <c r="C147">
-        <v>146.01</v>
+        <v>-146.01</v>
       </c>
       <c r="D147" t="s">
         <v>59</v>
@@ -2635,7 +2635,7 @@
         <v>49</v>
       </c>
       <c r="C148">
-        <v>481.53</v>
+        <v>-481.53</v>
       </c>
       <c r="D148" t="s">
         <v>57</v>
@@ -2649,7 +2649,7 @@
         <v>44</v>
       </c>
       <c r="C149">
-        <v>37.45</v>
+        <v>-37.45</v>
       </c>
       <c r="D149" t="s">
         <v>62</v>
@@ -2663,7 +2663,7 @@
         <v>50</v>
       </c>
       <c r="C150">
-        <v>127.13</v>
+        <v>-127.13</v>
       </c>
       <c r="D150" t="s">
         <v>64</v>
@@ -2677,7 +2677,7 @@
         <v>52</v>
       </c>
       <c r="C151">
-        <v>25.58</v>
+        <v>-25.58</v>
       </c>
       <c r="D151" t="s">
         <v>62</v>
@@ -2705,7 +2705,7 @@
         <v>53</v>
       </c>
       <c r="C153">
-        <v>299.47</v>
+        <v>-299.47</v>
       </c>
       <c r="D153" t="s">
         <v>58</v>
@@ -2719,7 +2719,7 @@
         <v>51</v>
       </c>
       <c r="C154">
-        <v>305.22</v>
+        <v>-305.22</v>
       </c>
       <c r="D154" t="s">
         <v>57</v>
@@ -2733,7 +2733,7 @@
         <v>41</v>
       </c>
       <c r="C155">
-        <v>36.84</v>
+        <v>-36.84</v>
       </c>
       <c r="D155" t="s">
         <v>62</v>
@@ -2747,7 +2747,7 @@
         <v>50</v>
       </c>
       <c r="C156">
-        <v>82.39</v>
+        <v>-82.39</v>
       </c>
       <c r="D156" t="s">
         <v>64</v>
@@ -2761,7 +2761,7 @@
         <v>40</v>
       </c>
       <c r="C157">
-        <v>75.09</v>
+        <v>-75.09</v>
       </c>
       <c r="D157" t="s">
         <v>60</v>
@@ -2775,7 +2775,7 @@
         <v>46</v>
       </c>
       <c r="C158">
-        <v>49.42</v>
+        <v>-49.42</v>
       </c>
       <c r="D158" t="s">
         <v>64</v>
@@ -2789,7 +2789,7 @@
         <v>42</v>
       </c>
       <c r="C159">
-        <v>130.23</v>
+        <v>-130.23</v>
       </c>
       <c r="D159" t="s">
         <v>63</v>
@@ -2803,7 +2803,7 @@
         <v>34</v>
       </c>
       <c r="C160">
-        <v>40.54</v>
+        <v>-40.54</v>
       </c>
       <c r="D160" t="s">
         <v>57</v>
@@ -2817,7 +2817,7 @@
         <v>48</v>
       </c>
       <c r="C161">
-        <v>944.1900000000001</v>
+        <v>-944.1900000000001</v>
       </c>
       <c r="D161" t="s">
         <v>63</v>
@@ -2831,7 +2831,7 @@
         <v>53</v>
       </c>
       <c r="C162">
-        <v>148.29</v>
+        <v>-148.29</v>
       </c>
       <c r="D162" t="s">
         <v>58</v>
@@ -2845,7 +2845,7 @@
         <v>40</v>
       </c>
       <c r="C163">
-        <v>79.90000000000001</v>
+        <v>-79.90000000000001</v>
       </c>
       <c r="D163" t="s">
         <v>60</v>
@@ -2859,7 +2859,7 @@
         <v>40</v>
       </c>
       <c r="C164">
-        <v>41.68</v>
+        <v>-41.68</v>
       </c>
       <c r="D164" t="s">
         <v>60</v>
@@ -2873,7 +2873,7 @@
         <v>39</v>
       </c>
       <c r="C165">
-        <v>64.89</v>
+        <v>-64.89</v>
       </c>
       <c r="D165" t="s">
         <v>58</v>
@@ -2887,7 +2887,7 @@
         <v>55</v>
       </c>
       <c r="C166">
-        <v>135.51</v>
+        <v>-135.51</v>
       </c>
       <c r="D166" t="s">
         <v>59</v>
@@ -2901,7 +2901,7 @@
         <v>44</v>
       </c>
       <c r="C167">
-        <v>45.98</v>
+        <v>-45.98</v>
       </c>
       <c r="D167" t="s">
         <v>62</v>
@@ -2915,7 +2915,7 @@
         <v>56</v>
       </c>
       <c r="C168">
-        <v>88.95</v>
+        <v>-88.95</v>
       </c>
       <c r="D168" t="s">
         <v>60</v>
@@ -2943,7 +2943,7 @@
         <v>40</v>
       </c>
       <c r="C170">
-        <v>74.33</v>
+        <v>-74.33</v>
       </c>
       <c r="D170" t="s">
         <v>60</v>
@@ -2957,7 +2957,7 @@
         <v>55</v>
       </c>
       <c r="C171">
-        <v>120.04</v>
+        <v>-120.04</v>
       </c>
       <c r="D171" t="s">
         <v>59</v>
@@ -2971,7 +2971,7 @@
         <v>41</v>
       </c>
       <c r="C172">
-        <v>2.76</v>
+        <v>-2.76</v>
       </c>
       <c r="D172" t="s">
         <v>62</v>
@@ -2985,7 +2985,7 @@
         <v>52</v>
       </c>
       <c r="C173">
-        <v>12.62</v>
+        <v>-12.62</v>
       </c>
       <c r="D173" t="s">
         <v>62</v>
@@ -2999,7 +2999,7 @@
         <v>35</v>
       </c>
       <c r="C174">
-        <v>114.58</v>
+        <v>-114.58</v>
       </c>
       <c r="D174" t="s">
         <v>58</v>
@@ -3013,7 +3013,7 @@
         <v>48</v>
       </c>
       <c r="C175">
-        <v>748.08</v>
+        <v>-748.08</v>
       </c>
       <c r="D175" t="s">
         <v>63</v>
@@ -3027,7 +3027,7 @@
         <v>41</v>
       </c>
       <c r="C176">
-        <v>11.23</v>
+        <v>-11.23</v>
       </c>
       <c r="D176" t="s">
         <v>62</v>
@@ -3041,7 +3041,7 @@
         <v>56</v>
       </c>
       <c r="C177">
-        <v>97.34</v>
+        <v>-97.34</v>
       </c>
       <c r="D177" t="s">
         <v>60</v>
@@ -3055,7 +3055,7 @@
         <v>40</v>
       </c>
       <c r="C178">
-        <v>85.95999999999999</v>
+        <v>-85.95999999999999</v>
       </c>
       <c r="D178" t="s">
         <v>60</v>
@@ -3069,7 +3069,7 @@
         <v>55</v>
       </c>
       <c r="C179">
-        <v>137.49</v>
+        <v>-137.49</v>
       </c>
       <c r="D179" t="s">
         <v>59</v>
@@ -3083,7 +3083,7 @@
         <v>41</v>
       </c>
       <c r="C180">
-        <v>3.77</v>
+        <v>-3.77</v>
       </c>
       <c r="D180" t="s">
         <v>62</v>
@@ -3097,7 +3097,7 @@
         <v>41</v>
       </c>
       <c r="C181">
-        <v>3.11</v>
+        <v>-3.11</v>
       </c>
       <c r="D181" t="s">
         <v>62</v>
@@ -3111,7 +3111,7 @@
         <v>48</v>
       </c>
       <c r="C182">
-        <v>691.88</v>
+        <v>-691.88</v>
       </c>
       <c r="D182" t="s">
         <v>63</v>
@@ -3125,7 +3125,7 @@
         <v>37</v>
       </c>
       <c r="C183">
-        <v>15.69</v>
+        <v>-15.69</v>
       </c>
       <c r="D183" t="s">
         <v>60</v>
@@ -3139,7 +3139,7 @@
         <v>48</v>
       </c>
       <c r="C184">
-        <v>3.14</v>
+        <v>-3.14</v>
       </c>
       <c r="D184" t="s">
         <v>63</v>
@@ -3153,7 +3153,7 @@
         <v>43</v>
       </c>
       <c r="C185">
-        <v>118.98</v>
+        <v>-118.98</v>
       </c>
       <c r="D185" t="s">
         <v>64</v>
@@ -3167,7 +3167,7 @@
         <v>41</v>
       </c>
       <c r="C186">
-        <v>49.03</v>
+        <v>-49.03</v>
       </c>
       <c r="D186" t="s">
         <v>62</v>
@@ -3181,7 +3181,7 @@
         <v>44</v>
       </c>
       <c r="C187">
-        <v>34.02</v>
+        <v>-34.02</v>
       </c>
       <c r="D187" t="s">
         <v>62</v>
@@ -3223,7 +3223,7 @@
         <v>51</v>
       </c>
       <c r="C190">
-        <v>494.22</v>
+        <v>-494.22</v>
       </c>
       <c r="D190" t="s">
         <v>57</v>
@@ -3237,7 +3237,7 @@
         <v>46</v>
       </c>
       <c r="C191">
-        <v>176.62</v>
+        <v>-176.62</v>
       </c>
       <c r="D191" t="s">
         <v>64</v>
@@ -3265,7 +3265,7 @@
         <v>46</v>
       </c>
       <c r="C193">
-        <v>60.14</v>
+        <v>-60.14</v>
       </c>
       <c r="D193" t="s">
         <v>64</v>
@@ -3279,7 +3279,7 @@
         <v>48</v>
       </c>
       <c r="C194">
-        <v>906.54</v>
+        <v>-906.54</v>
       </c>
       <c r="D194" t="s">
         <v>63</v>
@@ -3293,7 +3293,7 @@
         <v>53</v>
       </c>
       <c r="C195">
-        <v>226.15</v>
+        <v>-226.15</v>
       </c>
       <c r="D195" t="s">
         <v>58</v>
@@ -3307,7 +3307,7 @@
         <v>40</v>
       </c>
       <c r="C196">
-        <v>35.49</v>
+        <v>-35.49</v>
       </c>
       <c r="D196" t="s">
         <v>60</v>
@@ -3321,7 +3321,7 @@
         <v>52</v>
       </c>
       <c r="C197">
-        <v>26.92</v>
+        <v>-26.92</v>
       </c>
       <c r="D197" t="s">
         <v>62</v>
@@ -3335,7 +3335,7 @@
         <v>40</v>
       </c>
       <c r="C198">
-        <v>88.91</v>
+        <v>-88.91</v>
       </c>
       <c r="D198" t="s">
         <v>60</v>
@@ -3363,7 +3363,7 @@
         <v>42</v>
       </c>
       <c r="C200">
-        <v>923.5599999999999</v>
+        <v>-923.5599999999999</v>
       </c>
       <c r="D200" t="s">
         <v>63</v>
